--- a/output/base_final/consolidado_por_grupo/Grupo_11_DEMOLICIONES_consolidado.xlsx
+++ b/output/base_final/consolidado_por_grupo/Grupo_11_DEMOLICIONES_consolidado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB127"/>
+  <dimension ref="A1:X127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,50 +509,30 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>departamento_2</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>provincia_2</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>distrito_2</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>ubigeo</t>
+          <t>area</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
-        <is>
-          <t>dre</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>ugel</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>nombre_ie_2</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -635,50 +615,30 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UMACHULCO</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>UMACHULCO</t>
+          <t>UGEL CASTILLA</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>UGEL CASTILLA</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>40459 SAN ROQUE/40459 SAN ROQUE</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -761,50 +721,30 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHALLA</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>CHALLA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>40444</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -887,50 +827,30 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ARCATA</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ARCATA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ARCATA/40568/40568</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1013,50 +933,30 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHOCÑEHUAQUE</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>CHOCÑEHUAQUE</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>CHOCÑIHUAQUI/40577/40577</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1139,50 +1039,30 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>SULPUMAYO</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SULPUMAYO</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>40592</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1265,50 +1145,30 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHAIÑA</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>CHAIÑA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>40613</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1391,50 +1251,30 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYARANI</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>CAYARANI</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1517,50 +1357,30 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>UMACHULCO</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>UMACHULCO</t>
+          <t>UGEL CASTILLA</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>UGEL CASTILLA</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>UMACHULCO</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1643,50 +1463,30 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CHALLA</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>CHALLA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>CHALLA</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1769,50 +1569,30 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>VISCA VISCA</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>040603</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>VISCA VISCA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>040603</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>VISCA VISCA</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Cayarani</t>
         </is>
@@ -1901,50 +1681,30 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>070107</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>MI PERU</t>
+          <t>DRE CALLAO</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>MI PERU</t>
+          <t>UGEL VENTANILLA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>070107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
-        <is>
-          <t>DRE CALLAO</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>UGEL VENTANILLA</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>FE Y ALEGRIA 33/FE Y ALEGRIA 33/FE Y ALEGRIA 33</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
@@ -2037,50 +1797,30 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>SONGOÑA</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>CANCHIS</t>
+          <t>080606</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SAN PABLO</t>
+          <t>DRE CUSCO</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SONGOÑA</t>
+          <t>UGEL CANCHIS</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>080606</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
-        <is>
-          <t>DRE CUSCO</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>UGEL CANCHIS</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Pablo</t>
         </is>
@@ -2173,50 +1913,30 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCHACUAY</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>ANGARAES</t>
+          <t>090309</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>JULCAMARCA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ANCHACUAY</t>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>090309</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
-        <is>
-          <t>DRE HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>UGEL ANGARAES</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>36415</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
@@ -2309,50 +2029,30 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>MANYACCLLA</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>ANGARAES</t>
+          <t>090309</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>JULCAMARCA</t>
+          <t>DRE HUANCAVELICA</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>MANYACCLLA</t>
+          <t>UGEL ANGARAES</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>090309</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
-        <is>
-          <t>DRE HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>UGEL ANGARAES</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>36542</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
@@ -2445,50 +2145,30 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>CARAMARCA</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>LAURICOCHA</t>
+          <t>101006</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>DRE HUANUCO</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>CARAMARCA</t>
+          <t>UGEL LAURICOCHA</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
-        <is>
-          <t>DRE HUANUCO</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>UGEL LAURICOCHA</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>GUZMAN SERAFICO SOTO/GUZMAN SERAFICO SOTO</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Francisco de Asis</t>
         </is>
@@ -2581,50 +2261,30 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>MOCHE</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>1613 MI DULCE HOGAR</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -2717,50 +2377,30 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CURVA DE SUN</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>MOCHE</t>
+          <t>GRE LA LIBERTAD</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>CURVA DE SUN</t>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
-        <is>
-          <t>GRE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>80082 SAN FRANCISCO DE ASIS</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
@@ -2851,50 +2491,30 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>RINCONADA DEL PURUHUAY</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>150119</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>LURIN</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>RINCONADA DEL PURUHUAY</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>150119</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>6012/6012</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
@@ -2985,50 +2605,30 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>LIMA METROPOLITANA</t>
+          <t>SAN BARTOLO</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>150129</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SAN BARTOLO</t>
+          <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SAN BARTOLO</t>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>150129</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
-        <is>
-          <t>DRE LIMA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>6013 VIRGEN INMACULADA DEL ROSARIO</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
         <is>
           <t>Anexo 2 - DREML - UGEL 01 - LIMA METROPOLITANA</t>
         </is>
@@ -3117,50 +2717,30 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>ALTO PERILLO</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>160604</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>PAMPA HERMOSA</t>
+          <t>DRE LORETO</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>ALTO PERILLO</t>
+          <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>160604</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
-        <is>
-          <t>DRE LORETO</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>UGEL UCAYALI-CONTAMANA</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>64249</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pampa Hermosa</t>
         </is>
@@ -3253,50 +2833,30 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BOCA DEL MANU</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>BOCA DEL MANU</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>345 BOCA MANU</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3389,50 +2949,30 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3525,50 +3065,30 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>DIAMANTE</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3661,50 +3181,30 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SARIGUEMINIKI</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>SARIGUEMINIKI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>52245</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3797,50 +3297,30 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>YOMIBATO</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>YOMIBATO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -3933,50 +3413,30 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TAYACOME</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>TAYACOME</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4061,50 +3521,30 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVO EDEN</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>NUEVO EDEN</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4197,50 +3637,30 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO AZUL</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>PUERTO AZUL</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4333,50 +3753,30 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DIAMANTE NUEVO</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>FITZCARRALD</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>DIAMANTE NUEVO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>50843</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4461,50 +3861,30 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUENTE INAMBARI</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>PUENTE INAMBARI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4597,50 +3977,30 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUENTE INAMBARI</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>PUENTE INAMBARI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>52200</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4733,50 +4093,30 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRANCO CHICO</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>BARRANCO CHICO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>52133</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4869,50 +4209,30 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CAYCHIHUE ALTO Y QUEBRADA NUEVA</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>CAYCHIHUE ALTO Y QUEBRADA NUEVA</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>CIENCIAS DE NUEVA/52159 CIENCIAS DE NUEVA</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -4997,50 +4317,30 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>HUAYPETUE</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>HUAYPETUE</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>332 DOCE DE ENERO</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5125,50 +4425,30 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO PUNKIRI</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>PUERTO PUNKIRI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5261,50 +4541,30 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRANCO CHICO</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>HUEPETUHE</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>BARRANCO CHICO</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5389,50 +4649,30 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5517,50 +4757,30 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5645,50 +4865,30 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5773,50 +4973,30 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>53004 MIGUEL GRAU</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -5901,50 +5081,30 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAHUARA</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>PACAHUARA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>EL ARCA DE PACAHUARA/52216 EL ARCA DE PACAHUARA</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -6029,50 +5189,30 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -6149,50 +5289,30 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAHUARA</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>PACAHUARA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -6277,50 +5397,30 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BAMBU</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170302</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>BAMBU</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>170302</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -6413,50 +5513,30 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MAZUKO</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>PUERTO MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6549,50 +5629,30 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6685,50 +5745,30 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PALMERA</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>PALMERA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>52077/52077</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6821,50 +5861,30 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>52128</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -6957,50 +5977,30 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MAZUKO</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>PUERTO MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>52129</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7085,50 +6085,30 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>KOTSIMBA</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>KOTSIMBA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>440/52201</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7221,50 +6201,30 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SARAYACU</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SARAYACU</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>RICARDO PALMA SORIANO/52187 RICARDO PALMA SORIANO</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7349,50 +6309,30 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>ALTO LIBERTAD</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7485,50 +6425,30 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7621,50 +6541,30 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PONAL</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>PONAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>368 NIÑOS DE LA SELVA</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7749,50 +6649,30 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>2 DE MAYO</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2 DE MAYO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -7877,50 +6757,30 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CENTROMIN</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>CENTROMIN</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8005,50 +6865,30 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA CANDELARIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8133,50 +6973,30 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MAZUKO</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>MAZUKO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8269,50 +7089,30 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SOL NACIENTE</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>SOL NACIENTE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8397,50 +7197,30 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALTO LIBERTAD</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>ALTO LIBERTAD</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>ALTO LIBERTAD</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8533,50 +7313,30 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVA AREQUIPA</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NUEVA AREQUIPA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>NUEVA AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8661,50 +7421,30 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA RITA BAJA</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170102</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>INAMBARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SANTA RITA BAJA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>170102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>376 HORMIGUITAS ESCRITORAS</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -8789,50 +7529,30 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BELGICA</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>BELGICA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>52055</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -8917,50 +7637,30 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>IÑAPARI</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>IÑAPARI</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -9053,50 +7753,30 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BELGICA</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170301</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>IÑAPARI</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>BELGICA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>170301</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -9181,50 +7861,30 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>52062 JAVIER HERAUD/52062 JAVIER HERAUD</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9309,50 +7969,30 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FLORIDA ALTA</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>FLORIDA ALTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>52033/52033</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9437,50 +8077,30 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FLORIDA BAJA</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>FLORIDA BAJA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>52105</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9565,50 +8185,30 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>SANTO DOMINGO/SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9693,50 +8293,30 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>AMARAKAERI</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>AMARAKAERI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9821,50 +8401,30 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>JAVIER HERAUD</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -9957,50 +8517,30 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LABERINTO</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>52262 CARLOS MARQUEZ BRAGA</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10085,50 +8625,30 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>LABERINTO</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10221,50 +8741,30 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10357,50 +8857,30 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>JORGE CHAVEZ RENGIFO/JORGE CHAVEZ RENGIFO</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10493,50 +8973,30 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MAVILA</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>MAVILA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>HEROES DE ILLAMPU/HEROES DE ILLAMPU/HEROES DE ILLAMPU</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10621,50 +9081,30 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ALEGRIA</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>ALEGRIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>RAUL VARGAS QUIROZ/RAUL VARGAS QUIROZ</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10757,50 +9197,30 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SUDADERO</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SUDADERO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>52095/52095</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -10885,50 +9305,30 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>FRAY MARTIN</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>FRAY MARTIN</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>52136</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11021,50 +9421,30 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO NUEVO</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>PUERTO NUEVO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>52242</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11157,50 +9537,30 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TIPISHKA</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>TIPISHKA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>52137</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11293,50 +9653,30 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PLANCHON</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>PLANCHON</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11429,50 +9769,30 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO LUCERNA</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>PUERTO LUCERNA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11557,50 +9877,30 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ASOCIACION VILLA TERRASOL</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>ASOCIACION VILLA TERRASOL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11693,50 +9993,30 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BAJO MADRE DE DIOS</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>LAS PIEDRAS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>BAJO MADRE DE DIOS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>52081</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -11821,50 +10101,30 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JUAN GRANDE</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SAN JUAN GRANDE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -11957,50 +10217,30 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JOSE DE KARENE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SAN JOSE DE KARENE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>52075</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12093,50 +10333,30 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAL GUACAMAYO</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>PACAL GUACAMAYO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>52154</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12229,50 +10449,30 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN JUAN GRANDE</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SAN JUAN GRANDE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>PEDRO PAULET/PEDRO PAULET</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12365,50 +10565,30 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PACAL</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>PACAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12501,50 +10681,30 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DELTA 1 / BAJO PUKIRI</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>DELTA 1 / BAJO PUKIRI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>DANIEL ALCIDES CARRION/DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12629,50 +10789,30 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BOCA ISIRI</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>BOCA ISIRI</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12765,50 +10905,30 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>279 NIÑO DE PRAGA</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -12893,50 +11013,30 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>316 NIÑO JESUS</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -13021,50 +11121,30 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SHIPITIARI</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SHIPITIARI</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -13149,50 +11229,30 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SALVACION</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>170201</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>MANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SALVACION</t>
+          <t>UGEL MANU</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>UGEL MANU</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
@@ -13277,50 +11337,30 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN LORENZO</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SAN LORENZO</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -13405,50 +11445,30 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>52061/52061</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -13533,50 +11553,30 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -13661,50 +11661,30 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -13797,50 +11777,30 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>NUEVO PACARAN</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>NUEVO PACARAN</t>
+          <t>UGEL TAHUAMANU</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>UGEL TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
@@ -13925,50 +11885,30 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>OTILIA</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>OTILIA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14061,50 +12001,30 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>296 LAS PALMERAS</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14197,50 +12117,30 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14333,50 +12233,30 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO PARDO</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>PUERTO PARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14469,50 +12349,30 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>TRES ISLAS</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>TRES ISLAS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14605,50 +12465,30 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PALMA REAL</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>PALMA REAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14741,50 +12581,30 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>318 MI PEQUEÑO MUNDO</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14869,50 +12689,30 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>LAS ARDILLITAS</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -14997,50 +12797,30 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LA PASTORA</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>LA PASTORA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>LA PASTORA/LA PASTORA/LA PASTORA</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15125,50 +12905,30 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN BERNARDO</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SAN BERNARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>SAN BERNARDO/52035</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15253,50 +13013,30 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SONENE</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>SONENE</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>52084</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15389,50 +13129,30 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>BARRIO LINDO</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>BARRIO LINDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>52166 NUESTRA SEÑORA DE FATIMA/52166 NUESTRA SEÑORA DE FATIMA</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15525,50 +13245,30 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>ROMPE OLAS</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>ROMPE OLAS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>433 ROBERTO GUILLERMO VELA VALLES/52183/52183</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15661,50 +13361,30 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUERTO MALDONADO</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>PUERTO MALDONADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>SANTA RITA DE CASIA</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15797,50 +13477,30 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MONTE SALVADO</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MONTE SALVADO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>52225</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -15933,50 +13593,30 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CHONTA</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>CHONTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>52028</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16069,50 +13709,30 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MIRAFLORES</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16205,50 +13825,30 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>EL CASTAÑAL</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>EL CASTAÑAL</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16341,50 +13941,30 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>JORGE CHAVEZ RENGIFO</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ RENGIFO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>400 LUCECITAS DEL SABER</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16469,50 +14049,30 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>JOSE ALDAMIS</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>JOSE ALDAMIS</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16605,50 +14165,30 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>SAN BERNARDO</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>SAN BERNARDO</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16741,50 +14281,30 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>CHONTA</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>TAMBOPATA</t>
+          <t>DRE MADRE DE DIOS</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>CHONTA</t>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>170101</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
-        <is>
-          <t>DRE MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>UGEL TAMBOPATA</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>52028</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -16873,50 +14393,30 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>TOMASIRI</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230105</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>INCLAN</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>TOMASIRI</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>230105</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>42053 BARTOLOME JULIO ROSPIGLIOSI</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -17005,50 +14505,30 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PROTER</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230105</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>INCLAN</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>PROTER</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>230105</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>443 SANTA TERESITA/443 SANTA TERESITA</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -17136,45 +14616,25 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>230101</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>DRE TACNA</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>UGEL TACNA</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
-        <is>
-          <t>DRE TACNA</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>UGEL TACNA</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
